--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>442.35</v>
+        <v>438.4639</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04532999992370605</v>
+        <v>0.04565000057220459</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186474149.284503</v>
+        <v>5186474043.477695</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>442.35</v>
+        <v>438.4639</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2294236839936</v>
+        <v>2274081636352</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>38.5</v>
+        <v>38.16</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>5.56</v>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>479632850944</v>
+        <v>481139425280</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>56.937088</v>
+        <v>56.90141</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>48.731</v>
+        <v>50.286</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>15.573</v>
+        <v>16.069</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>18172774400</v>
+        <v>17668352000</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>42.13506</v>
+        <v>40.965515</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>13.714</v>
+        <v>14.802</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.318</v>
+        <v>2.502</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>705453096960</v>
+        <v>697351602176</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>61.962082</v>
+        <v>61.52125</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>2980.313</v>
+        <v>3040.311</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1123.777</v>
+        <v>1146.4</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>96707166208</v>
+        <v>94010572800</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>68.8736</v>
+        <v>66.953125</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>2.084</v>
+        <v>2.142</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.391</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1924108124160</v>
+        <v>1909692694528</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>67.18106</v>
+        <v>66.67774</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>45.017</v>
+        <v>46.421</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>25.104</v>
+        <v>25.887</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>4421031936</v>
+        <v>4448369152</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>52.01351</v>
+        <v>52.335133</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>20.312</v>
+        <v>20.783</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>2.587</v>
+        <v>2.647</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>446854037504</v>
+        <v>441839255552</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>67.41887</v>
+        <v>66.66226</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>52.959</v>
+        <v>56.149</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>19.169</v>
+        <v>20.323</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1551839789056</v>
+        <v>1687822925824</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>22.230547</v>
+        <v>24.20495</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>14.057</v>
+        <v>14.716</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>7.148</v>
+        <v>7.483</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>438.4639</v>
+        <v>434.11</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04565000057220459</v>
+        <v>0.04568999767303467</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186474043.477695</v>
+        <v>5186473538.743636</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>438.4639</v>
+        <v>434.11</v>
       </c>
     </row>
     <row r="38">
@@ -1434,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2274081636352</v>
+        <v>2251500027904</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>38.16</v>
+        <v>37.75</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>481139425280</v>
+        <v>478360567808</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>56.90141</v>
+        <v>56.839622</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>50.286</v>
+        <v>51.47</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>16.069</v>
+        <v>16.448</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17668352000</v>
+        <v>17467576320</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>40.965515</v>
+        <v>40.5</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.802</v>
+        <v>14.452</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.502</v>
+        <v>2.443</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>697351602176</v>
+        <v>692718862336</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>61.52125</v>
+        <v>60.967434</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>3040.311</v>
+        <v>3028.632</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1146.4</v>
+        <v>1141.997</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>94010572800</v>
+        <v>93593731072</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>66.953125</v>
+        <v>66.65625</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>2.142</v>
+        <v>2.132</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.401</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1909692694528</v>
+        <v>1902889402368</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>66.67774</v>
+        <v>66.66167</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>46.421</v>
+        <v>46.292</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>25.887</v>
+        <v>25.816</v>
       </c>
     </row>
     <row r="11">
@@ -1652,122 +1652,98 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>4448369152</v>
+        <v>4428153344</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>52.335133</v>
+        <v>52.097294</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>20.783</v>
+        <v>21.149</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>2.647</v>
+        <v>2.694</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>441839255552</v>
+        <v>1698738339840</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>66.66226</v>
+        <v>24.33491</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>56.149</v>
+        <v>15.592</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>20.323</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="n">
-        <v>1687822925824</v>
-      </c>
-      <c r="D13" s="33" t="n">
-        <v>24.20495</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>14.716</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>7.483</v>
+        <v>7.928</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D14" s="34">
+        <f>MEDIAN(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="E14" s="34">
+        <f>MEDIAN(E6:E12)</f>
+        <v/>
+      </c>
+      <c r="F14" s="34">
+        <f>MEDIAN(F6:F12)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Peer median</t>
+          <t>Peer mean</t>
         </is>
       </c>
       <c r="D15" s="34">
-        <f>MEDIAN(D6:D13)</f>
+        <f>AVERAGE(D6:D12)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>MEDIAN(E6:E13)</f>
+        <f>AVERAGE(E6:E12)</f>
         <v/>
       </c>
       <c r="F15" s="34">
-        <f>MEDIAN(F6:F13)</f>
+        <f>AVERAGE(F6:F12)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Peer mean</t>
-        </is>
-      </c>
-      <c r="D16" s="34">
-        <f>AVERAGE(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E16" s="34">
-        <f>AVERAGE(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F16" s="34">
-        <f>AVERAGE(F6:F13)</f>
-        <v/>
+          <t>Target percentile vs peers</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F16" s="35" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Target percentile vs peers</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1667,83 +1667,107 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lam Research Corporation</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>438112518144</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>66.22495000000001</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>55.697</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>20.16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Meta Platforms, Inc.</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C13" s="32" t="n">
         <v>1698738339840</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D13" s="33" t="n">
         <v>24.33491</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E13" s="33" t="n">
         <v>15.592</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F13" s="33" t="n">
         <v>7.928</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D14" s="34">
-        <f>MEDIAN(D6:D12)</f>
-        <v/>
-      </c>
-      <c r="E14" s="34">
-        <f>MEDIAN(E6:E12)</f>
-        <v/>
-      </c>
-      <c r="F14" s="34">
-        <f>MEDIAN(F6:F12)</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Peer mean</t>
+          <t>Peer median</t>
         </is>
       </c>
       <c r="D15" s="34">
-        <f>AVERAGE(D6:D12)</f>
+        <f>MEDIAN(D6:D13)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>AVERAGE(E6:E12)</f>
+        <f>MEDIAN(E6:E13)</f>
         <v/>
       </c>
       <c r="F15" s="34">
-        <f>AVERAGE(F6:F12)</f>
+        <f>MEDIAN(F6:F13)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="D16" s="34">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E17" s="35" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F17" s="35" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>434.11</v>
+        <v>423.71</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04568999767303467</v>
+        <v>0.04609000205993653</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186473538.743636</v>
+        <v>5186473968.629487</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>434.11</v>
+        <v>423.71</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2251500027904</v>
+        <v>2197560885248</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>37.75</v>
+        <v>36.84</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>5.52</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>478360567808</v>
+        <v>454700564480</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>56.839622</v>
+        <v>54.0283</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>51.47</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17467576320</v>
+        <v>16300096512</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>40.5</v>
+        <v>37.793106</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>14.452</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>692718862336</v>
+        <v>667615821824</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>60.967434</v>
+        <v>58.758068</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>3028.632</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>93593731072</v>
+        <v>89041289216</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>66.65625</v>
+        <v>63.414062</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>2.132</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1902889402368</v>
+        <v>1840327294976</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>66.66167</v>
+        <v>64.47</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>46.292</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>4428153344</v>
+        <v>4270103808</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>52.097294</v>
+        <v>50.23784</v>
       </c>
       <c r="E11" s="33" t="n">
         <v>21.149</v>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>438112518144</v>
+        <v>411018919936</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>66.22495000000001</v>
+        <v>62.12949</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>55.697</v>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1698738339840</v>
+        <v>1678710145024</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>24.33491</v>
+        <v>24.048</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>15.592</v>

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-14 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>423.71</v>
+        <v>422.31</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04609000205993653</v>
+        <v>0.04586999893188477</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186473968.629487</v>
+        <v>5186473819.213374</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>423.71</v>
+        <v>422.31</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2197560885248</v>
+        <v>2190299758592</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>36.84</v>
+        <v>37.81</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.52</v>
+        <v>5.34</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.84</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>454700564480</v>
+        <v>474624950272</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>54.0283</v>
+        <v>56.18374</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>51.47</v>
+        <v>49.15</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>16.448</v>
+        <v>15.706</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>16300096512</v>
+        <v>17348595712</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>37.793106</v>
+        <v>40.224136</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.452</v>
+        <v>13.537</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.443</v>
+        <v>2.288</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>667615821824</v>
+        <v>688163258368</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>58.758068</v>
+        <v>60.484417</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>3028.632</v>
+        <v>2908.501</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1141.997</v>
+        <v>1096.699</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>89041289216</v>
+        <v>89140019200</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>63.414062</v>
+        <v>63.48438</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>2.132</v>
+        <v>2.095</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.399</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1840327294976</v>
+        <v>1866374971392</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>64.47</v>
+        <v>65.49166</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>46.292</v>
+        <v>44.493</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>25.816</v>
+        <v>24.812</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>4270103808</v>
+        <v>4337183232</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>50.23784</v>
+        <v>51.027027</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>21.149</v>
+        <v>20.201</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>2.694</v>
+        <v>2.573</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>411018919936</v>
+        <v>434435883008</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>62.12949</v>
+        <v>65.793564</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>55.697</v>
+        <v>52.444</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>20.16</v>
+        <v>18.982</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1678710145024</v>
+        <v>1685081554944</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>24.048</v>
+        <v>24.12173</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>15.592</v>
+        <v>15.302</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>7.928</v>
+        <v>7.781</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-14 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>422.31</v>
+        <v>418.11</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04586999893188477</v>
+        <v>0.04549000263214111</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186473819.213374</v>
+        <v>5186473678.448256</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>422.31</v>
+        <v>418.11</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2190299758592</v>
+        <v>2168516509696</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>37.81</v>
+        <v>36.29</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>474624950272</v>
+        <v>454994329600</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>56.18374</v>
+        <v>54.063206</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>49.15</v>
+        <v>50.888</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>15.706</v>
+        <v>16.262</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17348595712</v>
+        <v>16498394112</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>40.224136</v>
+        <v>38.252872</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>13.537</v>
+        <v>14.396</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.288</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>688163258368</v>
+        <v>687444459520</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>60.484417</v>
+        <v>60.503223</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>2908.501</v>
+        <v>2992.094</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1096.699</v>
+        <v>1128.219</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>89140019200</v>
+        <v>88372133888</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>63.48438</v>
+        <v>62.9375</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>2.095</v>
+        <v>2.091</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1866374971392</v>
+        <v>1865447243776</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>65.49166</v>
+        <v>65.45910000000001</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>44.493</v>
+        <v>45.065</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>24.812</v>
+        <v>25.131</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>4337183232</v>
+        <v>4356020224</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>51.027027</v>
+        <v>51.248646</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>20.201</v>
+        <v>20.859</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>2.573</v>
+        <v>2.657</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>434435883008</v>
+        <v>411637972992</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>65.793564</v>
+        <v>62.10566</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>52.444</v>
+        <v>55.023</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>18.982</v>
+        <v>19.916</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1685081554944</v>
+        <v>1710592753664</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>24.12173</v>
+        <v>24.504728</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>15.302</v>
+        <v>15.402</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>7.781</v>
+        <v>7.832</v>
       </c>
     </row>
     <row r="15">
